--- a/data/csv/Consumer Staples.xlsx
+++ b/data/csv/Consumer Staples.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfpin\Desktop\Projects\gravity\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68AFE4EB-1232-4678-81AE-206C8928CD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531D9A52-0E52-44E0-8B69-33BF15BE6B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C6B9651D-6DD0-4C0C-8F9B-4D9453646C41}"/>
   </bookViews>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Ticker</t>
   </si>
   <si>
     <t>ADM</t>
-  </si>
-  <si>
-    <t>BF.B</t>
   </si>
   <si>
     <t>BG</t>
@@ -518,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F41344-378A-4AC9-8004-648DC9B8B7A2}">
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -701,11 +698,6 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
